--- a/BWI/bestwine_output/bestwine_Philippines.xlsx
+++ b/BWI/bestwine_output/bestwine_Philippines.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA93"/>
+  <dimension ref="A1:AA96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -10442,6 +10442,321 @@
       <c r="Z93" s="2" t="inlineStr"/>
       <c r="AA93" s="2" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr"/>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Versoza</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-versoza-7198a8186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>Alessandro Mazzocco</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alessandromazzocco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>Arlene Eustaquio</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Associate</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arlene-eustaquio-b37374110/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Philippines.xlsx
+++ b/BWI/bestwine_output/bestwine_Philippines.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA96"/>
+  <dimension ref="A1:AA101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -10757,6 +10757,531 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr"/>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>Maria Raquel</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/maria-raquel-manzanillo-4871711a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr"/>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>Riz R.</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/riz-r-a1160833/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr"/>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Versoza</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr"/>
+      <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-versoza-7198a8186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr"/>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>Alessandro Mazzocco</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr"/>
+      <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alessandromazzocco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr"/>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>Arlene Eustaquio</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Associate</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr"/>
+      <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arlene-eustaquio-b37374110/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Philippines.xlsx
+++ b/BWI/bestwine_output/bestwine_Philippines.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA101"/>
+  <dimension ref="A1:AA106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11282,6 +11282,531 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr"/>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>Maria Raquel</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr"/>
+      <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/maria-raquel-manzanillo-4871711a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr"/>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>Riz R.</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr"/>
+      <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/riz-r-a1160833/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr"/>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Versoza</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr"/>
+      <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-versoza-7198a8186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr"/>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>Alessandro Mazzocco</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr"/>
+      <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alessandromazzocco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr"/>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>Arlene Eustaquio</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Associate</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr"/>
+      <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arlene-eustaquio-b37374110/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Philippines.xlsx
+++ b/BWI/bestwine_output/bestwine_Philippines.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA106"/>
+  <dimension ref="A1:AA111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11807,6 +11807,531 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr"/>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>Maria Raquel</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr"/>
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/maria-raquel-manzanillo-4871711a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr"/>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>Riz R.</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr"/>
+      <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/riz-r-a1160833/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Versoza</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-versoza-7198a8186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr"/>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>Alessandro Mazzocco</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alessandromazzocco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr"/>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>Arlene Eustaquio</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Associate</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arlene-eustaquio-b37374110/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Philippines.xlsx
+++ b/BWI/bestwine_output/bestwine_Philippines.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA111"/>
+  <dimension ref="A1:AA116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12332,6 +12332,531 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr"/>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>Maria Raquel</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/maria-raquel-manzanillo-4871711a2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>La Peregrina Filipina Inc.</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>84143</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Baguio</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Cordillera Administrative Region, Benguet</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>4 Manzanillo</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>wine@laperegrinafilipina.com</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>010-301-834-000</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-peregrina-filipina-inc/</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/laperegrinafilipina</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/la.peregrina.filipina/</t>
+        </is>
+      </c>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr"/>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>Riz R.</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/riz-r-a1160833/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr"/>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>Patricia Versoza</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricia-versoza-7198a8186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>Alessandro Mazzocco</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alessandromazzocco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Winehub Inc.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>122282</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Makati</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Metro Manila</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>5046 P Burgos</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://winehub.ph</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>info@winehub.ph</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>010-742-062-000</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winehub-inc/</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehub.ph/</t>
+        </is>
+      </c>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>Arlene Eustaquio</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Associate</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arlene-eustaquio-b37374110/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
